--- a/app/ejemplos/DEXIAE_ejemplo_extraccion.xlsx
+++ b/app/ejemplos/DEXIAE_ejemplo_extraccion.xlsx
@@ -7,9 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extracción" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validación" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validación detalle" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validación'!$A$8:$J$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Validación'!$8:$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Validación detalle'!$A$1:$K$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,10 +33,62 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00075985"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00075985"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="005B21B6"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="005B21B6"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <color rgb="00475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <color rgb="002563EB"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -39,11 +97,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000056B3"/>
+        <fgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -52,30 +130,260 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="00D6DEE9"/>
+        <color rgb="00D9DEE5"/>
       </left>
       <right style="thin">
-        <color rgb="00D6DEE9"/>
+        <color rgb="00D9DEE5"/>
       </right>
       <top style="thin">
-        <color rgb="00D6DEE9"/>
+        <color rgb="00D9DEE5"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D6DEE9"/>
+        <color rgb="00D9DEE5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="002563EB"/>
+      </left>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="002563EB"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0094A3B8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0094A3B8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0094A3B8"/>
+      </left>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0094A3B8"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,16 +749,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -460,331 +760,1062 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>RUTA_RELATIVA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>CUIT</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Comprobante</t>
+          <t>FECHA</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>NUMERO</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ESTADO_PROCESO</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>VALIDACION</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>VALIDACION_DETALLE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>VALIDACION_NIVEL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>FC_DEMO_001.pdf</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>30-11111111-9</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>20123456786</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0001-00001231</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>184.525,00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FC_DEMO_002.pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>20123456786</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0001-00001232</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>96.800,00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FC_DEMO_003.pdf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>20123456786</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0001-00001233</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>412.300,50</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FC_DEMO_004.pdf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30111111119</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0001-00001234</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>38.450,00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1 hallazgo(s)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CUIT inválido (dígito verificador): 30111111119</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FC_DEMO_005.pdf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>20123456786</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0001-00001235</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1.250.000,00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FC_DEMO_006.pdf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>20123456786</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0001-00001236</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>57.900,00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FC_DEMO_007.pdf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20123456786</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0001-00001237</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>208.715,20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FC_DEMO_008.pdf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20123456786</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>0001-00001234</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>184525</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>FC_DEMO_002.pdf</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>30-11111111-9</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>0001-00001235</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>96800</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>FC_DEMO_003.pdf</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>30-22222222-8</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0003-00000871</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>45320.5</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>FC_DEMO_004.pdf</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>30-33333333-7</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0002-00004510</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>210000</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>FC_DEMO_005.pdf</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>30-11111111-9</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0001-00001236</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>78990</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>FC_DEMO_006.pdf</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>30-44444444-6</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0005-00000042</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>15600</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>FC_DEMO_007.pdf</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>30-33333333-7</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0002-00004511</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>132750</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>FC_DEMO_008.pdf</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>30-11111111-9</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0001-00001234</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>184525</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>DUPLICADO</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0001-00001238</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DATOS FALTANTES</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>FC_DEMO_009.pdf</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>30-55555555-5</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0009-00000108</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>9087</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20123456786</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0001-00001239</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>12.600,00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>FC_DEMO_010.pdf</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>30-22222222-8</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0003-00000872</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>145500</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20123456786</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0001-00001233</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>412.300,50</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1 hallazgo(s)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Duplicado lógico: CUIT+NUMERO repetido (igual que FC_DEMO_003.pdf)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Validación del lote</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Set: Estandar AR · 10 documento(s) mirado(s) por las reglas. Cada fila es un hallazgo. El # de cada hallazgo lleva a su evidencia, documento por documento, en «Validación detalle».</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>HALLAZGOS</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>GRUPOS</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>FALTA DE CORRESPONDENCIA</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>DUPLICIDAD · más de uno donde va uno solo</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>VALOR NO VÁLIDO · el dato no cumple la condición de la regla</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n"/>
+    </row>
+    <row r="6" ht="4" customHeight="1">
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+    </row>
+    <row r="7" ht="6" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>GRUPO</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>NIVEL</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>REGLA</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>QUÉ PASÓ</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>EVIDENCIA</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>DOCUMENTOS</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>REVISAR EN</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>QUÉ CONTROLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>VALOR NO VÁLIDO</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>CUIT tiene el dígito verificador mal.</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>CUIT: 30111111119</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>FC_DEMO_004</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>CUIT tiene que tener el dígito verificador correcto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28.75" customHeight="1">
+      <c r="A10" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>DUPLICIDAD</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>FC_DEMO_003 y FC_DEMO_010 comparten CUIT y NUMERO y la regla pide uno solo.</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>CUIT y NUMERO: 20123456786 · 0001-00001233</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>FC_DEMO_003 · FC_DEMO_010</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>Un solo documento por cada CUIT y NUMERO.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A8:J10"/>
+  <mergeCells count="10">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:D6"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E5:F6"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="H3:I3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A9" location="'Validación detalle'!A2"/>
+    <hyperlink ref="A10" location="'Validación detalle'!A3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="inlineStr">
+        <is>
+          <t>GRUPO</t>
+        </is>
+      </c>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t>NIVEL</t>
+        </is>
+      </c>
+      <c r="D1" s="22" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="E1" s="22" t="inlineStr">
+        <is>
+          <t>REGLA</t>
+        </is>
+      </c>
+      <c r="F1" s="22" t="inlineStr">
+        <is>
+          <t>DOCUMENTO</t>
+        </is>
+      </c>
+      <c r="G1" s="22" t="inlineStr">
+        <is>
+          <t>CAMPO</t>
+        </is>
+      </c>
+      <c r="H1" s="22" t="inlineStr">
+        <is>
+          <t>VALOR</t>
+        </is>
+      </c>
+      <c r="I1" s="22" t="inlineStr">
+        <is>
+          <t>ESTADO</t>
+        </is>
+      </c>
+      <c r="J1" s="22" t="inlineStr">
+        <is>
+          <t>ARCHIVO</t>
+        </is>
+      </c>
+      <c r="K1" s="22" t="inlineStr">
+        <is>
+          <t>RUTA_RELATIVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>VALOR NO VÁLIDO</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F2" s="25" t="inlineStr">
+        <is>
+          <t>FC_DEMO_004</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>CUIT</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>30111111119</t>
+        </is>
+      </c>
+      <c r="I2" s="26" t="inlineStr">
+        <is>
+          <t>NO VÁLIDO</t>
+        </is>
+      </c>
+      <c r="J2" s="24" t="inlineStr">
+        <is>
+          <t>FC_DEMO_004.pdf</t>
+        </is>
+      </c>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>DUPLICIDAD</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F3" s="29" t="inlineStr">
+        <is>
+          <t>FC_DEMO_003</t>
+        </is>
+      </c>
+      <c r="G3" s="28" t="inlineStr">
+        <is>
+          <t>CUIT + NUMERO</t>
+        </is>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>20123456786 · 0001-00001233</t>
+        </is>
+      </c>
+      <c r="I3" s="30" t="inlineStr">
+        <is>
+          <t>REPETIDO</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>FC_DEMO_003.pdf</t>
+        </is>
+      </c>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>DUPLICIDAD</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>FC_DEMO_010</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>CUIT + NUMERO</t>
+        </is>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>20123456786 · 0001-00001233</t>
+        </is>
+      </c>
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>REPETIDO</t>
+        </is>
+      </c>
+      <c r="J4" s="28" t="inlineStr">
+        <is>
+          <t>FC_DEMO_010.pdf</t>
+        </is>
+      </c>
+      <c r="K4" s="28" t="inlineStr">
+        <is>
+          <t>(carpeta raiz)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K4"/>
+  <hyperlinks>
+    <hyperlink ref="F2" location="'Sheet1'!A5"/>
+    <hyperlink ref="F3" location="'Sheet1'!A4"/>
+    <hyperlink ref="F4" location="'Sheet1'!A11"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/app/ejemplos/DEXIAE_ejemplo_extraccion.xlsx
+++ b/app/ejemplos/DEXIAE_ejemplo_extraccion.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validación" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validación detalle" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revisión" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validación'!$A$8:$J$10</definedName>
@@ -88,7 +89,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -120,8 +121,13 @@
         <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7E0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -300,11 +306,35 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0094A3B8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -384,6 +414,14 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,6 +496,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>DEXIAE</author>
+  </authors>
+  <commentList>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>Sin revisar: «TOTAL» es obligatorio y no se leyó nada.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -749,7 +802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,21 +841,6 @@
           <t>ESTADO_PROCESO</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>VALIDACION</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>VALIDACION_DETALLE</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>VALIDACION_NIVEL</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -840,16 +878,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -887,16 +915,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -934,16 +952,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -981,21 +989,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1 hallazgo(s)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CUIT inválido (dígito verificador): 30111111119</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1033,16 +1026,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1080,16 +1063,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1127,16 +1100,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1164,19 +1127,10 @@
           <t>0001-00001238</t>
         </is>
       </c>
+      <c r="F9" s="31" t="n"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>DATOS FALTANTES</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1216,16 +1170,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1263,24 +1207,10 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1 hallazgo(s)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Duplicado lógico: CUIT+NUMERO repetido (igual que FC_DEMO_003.pdf)</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1320,20 +1250,20 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="6" t="n"/>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="32" t="n">
         <v>2</v>
       </c>
       <c r="F3" s="6" t="n"/>
       <c r="G3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="H3" s="33" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="6" t="n"/>
@@ -1371,24 +1301,13 @@
           <t>DUPLICIDAD · más de uno donde va uno solo</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
       <c r="E5" s="14" t="inlineStr">
         <is>
           <t>VALOR NO VÁLIDO · el dato no cumple la condición de la regla</t>
         </is>
       </c>
-      <c r="F5" s="15" t="n"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="13" t="n"/>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-    </row>
+    </row>
+    <row r="6" ht="4" customHeight="1"/>
     <row r="7" ht="6" customHeight="1"/>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -1818,4 +1737,116 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>HORA (UTC)</t>
+        </is>
+      </c>
+      <c r="B1" s="34" t="inlineStr">
+        <is>
+          <t>USUARIO</t>
+        </is>
+      </c>
+      <c r="C1" s="34" t="inlineStr">
+        <is>
+          <t>EQUIPO</t>
+        </is>
+      </c>
+      <c r="D1" s="34" t="inlineStr">
+        <is>
+          <t>DOCUMENTO</t>
+        </is>
+      </c>
+      <c r="E1" s="34" t="inlineStr">
+        <is>
+          <t>CAMPO / REGLA</t>
+        </is>
+      </c>
+      <c r="F1" s="34" t="inlineStr">
+        <is>
+          <t>DECISIÓN</t>
+        </is>
+      </c>
+      <c r="G1" s="34" t="inlineStr">
+        <is>
+          <t>SE LEYÓ</t>
+        </is>
+      </c>
+      <c r="H1" s="34" t="inlineStr">
+        <is>
+          <t>EN EL EXCEL</t>
+        </is>
+      </c>
+      <c r="I1" s="34" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+      <c r="J1" s="34" t="inlineStr">
+        <is>
+          <t>HUELLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cabeza de la cadena</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(sin decisiones)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Qué prueba</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Trazabilidad local: detecta que se editó o se sacó una decisión de la base. Usuario y equipo son la sesión de Windows que decidió, no una firma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sin terminar</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Se generó con 1 caso(s) sin decidir, marcados en su hoja.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>